--- a/Day_7_Dynamic array.xlsx
+++ b/Day_7_Dynamic array.xlsx
@@ -1,25 +1,166 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f5c7b832c0e5f38/Documents/My projects/100-days-of-data-repository/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048A7095F46125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{941119BE-5D4C-46F8-9954-AD3BF86A0BFA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="32">
+  <si>
+    <t>DIVISION</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>Wencal</t>
+  </si>
+  <si>
+    <t>Blend</t>
+  </si>
+  <si>
+    <t>Game</t>
+  </si>
+  <si>
+    <t>Twistr</t>
+  </si>
+  <si>
+    <t>Utility</t>
+  </si>
+  <si>
+    <t>Rehire</t>
+  </si>
+  <si>
+    <t>Voltage</t>
+  </si>
+  <si>
+    <t>Inkly</t>
+  </si>
+  <si>
+    <t>Sleoops</t>
+  </si>
+  <si>
+    <t>Misty Wash</t>
+  </si>
+  <si>
+    <t>Kind Ape</t>
+  </si>
+  <si>
+    <t>Right App</t>
+  </si>
+  <si>
+    <t>Haloot</t>
+  </si>
+  <si>
+    <t>Perino</t>
+  </si>
+  <si>
+    <t>Dasring</t>
+  </si>
+  <si>
+    <t>Flowrrr</t>
+  </si>
+  <si>
+    <t>Baden</t>
+  </si>
+  <si>
+    <t>Jellyfish</t>
+  </si>
+  <si>
+    <t>Commuta</t>
+  </si>
+  <si>
+    <t>Five Labs</t>
+  </si>
+  <si>
+    <t>Silvrr</t>
+  </si>
+  <si>
+    <t>KryTis</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Dynamic</t>
+  </si>
+  <si>
+    <t>Array</t>
+  </si>
+  <si>
+    <t>obosonte</t>
+  </si>
+  <si>
+    <t>repete</t>
+  </si>
+  <si>
+    <t>Unique drop-down for Division</t>
+  </si>
+  <si>
+    <t>Dependent Drop down</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -66,6 +207,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F6C1892-19AC-42D9-AB98-F0F025DB69B5}" name="Table1" displayName="Table1" ref="A1:B33" totalsRowShown="0">
+  <autoFilter ref="A1:B33" xr:uid="{9F6C1892-19AC-42D9-AB98-F0F025DB69B5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9A7CAF38-05A6-416E-80FC-936EF8EDB93B}" name="DIVISION"/>
+    <tableColumn id="2" xr3:uid="{1A5E7D36-FE52-44E3-82A1-1B00D40753EE}" name="APP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +482,353 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="6" max="6" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="str" cm="1">
+        <f t="array" ref="H8:H18">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(Table1[[#All],[APP]],Table1[[#All],[DIVISION]]=F2))</f>
+        <v>Baden</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="str" cm="1">
+        <f t="array" ref="F9:F13">_xlfn._xlws.SORT(_xlfn.UNIQUE(Table1[DIVISION]))</f>
+        <v>Game</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Baden</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="str">
+        <v>New</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Commuta</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="str">
+        <v>obosonte</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Commuta</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Productivity</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Dasring</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Utility</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Jellyfish</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Kind Ape</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Perino</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Rehire</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Twistr</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Wencal</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{26B1108F-7591-4466-BFCA-481CB751ABA4}">
+      <formula1>$F$9:$F$13</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{6776EC34-7185-499A-925B-B7FC807F9E25}">
+      <formula1>_xlfn.ANCHORARRAY($H$8)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>